--- a/task259/golden/data_engineer_bands_2027.xlsx
+++ b/task259/golden/data_engineer_bands_2027.xlsx
@@ -27,7 +27,7 @@
     <t>Data Engineer pay bands from 1 April 2027</t>
   </si>
   <si>
-    <t>Market as in effect on 1 October 2026: matched Tallyband respondents, each report carried to the benchmark date at the market's movement at a fixed level (1.7 per cent a year). Filed to the nearest $1,000.</t>
+    <t>Market as in effect on 1 October 2026: matched Tallyband respondents, each report carried to the benchmark date at the movement of pay at a fixed level within employers (2.7 per cent a year). Filed to the nearest $1,000.</t>
   </si>
   <si>
     <t>Level</t>
@@ -589,7 +589,7 @@
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="7">
-        <v>117000</v>
+        <v>119000</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="8">
@@ -602,7 +602,7 @@
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="7">
-        <v>143000</v>
+        <v>145000</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="8">
@@ -614,13 +614,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="10">
-        <v>155000</v>
+        <v>158000</v>
       </c>
       <c r="C7" s="10">
-        <v>168000</v>
+        <v>170000</v>
       </c>
       <c r="D7" s="10">
-        <v>182000</v>
+        <v>183000</v>
       </c>
       <c r="E7" s="11">
         <v>1366</v>
@@ -632,7 +632,7 @@
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="7">
-        <v>201000</v>
+        <v>204000</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="8">
